--- a/AAII_Financials/Yearly/NSANY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NSANY_YR_FIN.xlsx
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>75518900</v>
+      </c>
+      <c r="E8" s="3">
         <v>84363200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>83869700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>79714000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>69375800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71090800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>91809300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>104451300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>112529300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>78993100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>89593000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>97030500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>96019900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>79422200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>85057600</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>60269700</v>
+      </c>
+      <c r="E9" s="3">
         <v>67545400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>65359700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>62068700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>52836900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>55658900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>71291500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>79874300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>85092900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>63508000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>72007900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>78828600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>79106300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>66266000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>70266400</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9685000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11308100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13665100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12892500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11150500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9501200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13345100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>17181200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20123000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15485100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>17585000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18201900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16913500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13156300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14791200</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,37 +899,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3537400</v>
+      </c>
+      <c r="E12" s="3">
         <v>4133800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4032400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3928400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3986200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4552400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5062800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4721000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4668600</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2776400</v>
+      </c>
+      <c r="E14" s="3">
         <v>4165600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>680500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>850100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-643100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1067900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5734800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>620800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>372500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1152100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>83000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>247200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>209700</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>334800</v>
+      </c>
+      <c r="E15" s="3">
         <v>470400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>424800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>448900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>472600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>499300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>605400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>512600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>517700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>354500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>368700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>398000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>415200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>437500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>487900</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>75154100</v>
+      </c>
+      <c r="E17" s="3">
         <v>83897100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>80109700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>76877100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>67339300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>72452900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>92185400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>101579500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>107117500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>74090600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>84914500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>92202200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>91537800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>75691400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>80332900</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>364800</v>
+      </c>
+      <c r="E18" s="3">
         <v>466100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3760000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2836800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2036600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1362100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-376100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2871800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5411800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4902500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4678500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4828300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4482000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3730800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4724700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>75300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1090100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-977000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1218800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-780700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>454800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-621200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1835700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1510800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1697900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>890900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1284200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>629700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>938200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>357800</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>624400</v>
+      </c>
+      <c r="E21" s="3">
         <v>2026600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5161800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4504500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3289800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1317700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>850500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5220100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7440300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12139200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11496900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12621900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11121200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9666900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10145900</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>715900</v>
+      </c>
+      <c r="E22" s="3">
         <v>516700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>515900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>474300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>460700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>329900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>101100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>121600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>119300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>95200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>182300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>248800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>262700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>239200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>297300</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2769600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2762100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3961700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3027300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3163900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3068100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5325400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4311100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6692200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6505200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5387100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5863700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4849100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4429900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4785100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>542700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1645900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>989500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1212900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1197700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>837200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>865700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1225500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-498200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1783700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1324000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1683200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1053900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1129800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1369600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3312300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4408000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2972100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1814400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1966300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3905400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6191100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3085600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7190400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4721500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4063000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4180500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3795200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3300000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3415500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3352700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4480200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2820700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1669300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1774900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4057000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6237900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2880100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7032600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4472000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3850200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3903100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3563600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3100800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3086600</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,8 +1733,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1688,12 +1748,15 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-75300</v>
+      </c>
+      <c r="E32" s="3">
         <v>1090100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>977000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1218800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>780700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-454800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>621200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1835700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1510800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1697900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-890900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1284200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-629700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-938200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-357800</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3352700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4480200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2820700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1669200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1774900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4057000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6238000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2880000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7032600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4472000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3850200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3903100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3563600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3100800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3086600</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3352700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4480200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2820700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1669200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1774900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4057000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6238000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2880000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7032600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4472000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3850200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3903100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3563600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3100800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3086600</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>12849300</v>
+        <v>13660800</v>
       </c>
       <c r="E41" s="3">
+        <v>14425200</v>
+      </c>
+      <c r="F41" s="3">
         <v>11798300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12670400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11054400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15775900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12036000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10575500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10108800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7565500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6753000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6492000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7537400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5493600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6919400</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1576000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>1558600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1624200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2969900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1466800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2421100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1258600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>670400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>819100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>539400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>355300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>123400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>978600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>700400</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3910300</v>
+      </c>
+      <c r="E43" s="3">
         <v>3726800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4000800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4217500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3121900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4536500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3231000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4548200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6853900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>54204900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>54420000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>60789600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>52766700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>42735500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>35931500</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10246500</v>
+      </c>
+      <c r="E44" s="3">
         <v>11167500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>13590300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>12812200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11236400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10303600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12457200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11352100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12151500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8581100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9368100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11174300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10551000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9501400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>9211500</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5778100</v>
+      </c>
+      <c r="E45" s="3">
         <v>5229100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5266000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5496200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5108700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5645100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6802400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8471300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7232800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6086900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7914300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9195800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7882500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6870900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6992300</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>79717700</v>
+      </c>
+      <c r="E46" s="3">
         <v>82294700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>85178000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>85517700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>84951600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>93578200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>99216900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>104802000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>108567300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>77257600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>78994700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>88007000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>78861000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>65580000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>59755100</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9141200</v>
+      </c>
+      <c r="E47" s="3">
         <v>9516800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9041200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8811100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8656300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10167600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10876500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12043300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11885400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7905100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6611600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8538100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8622000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13139300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3407000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12242600</v>
+      </c>
+      <c r="E48" s="3">
         <v>13670800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16299600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17811600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>18943700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19923000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19583400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23453400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24707500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35555000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38344200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44921000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>43583600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>38017500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>33730500</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1055100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1446100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1232800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1297500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>981500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1096000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1068100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1213500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1212600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>861400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>961900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>976300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>845800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1792000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1085800</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4408900</v>
+      </c>
+      <c r="E52" s="3">
         <v>3655000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2908100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2287800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2862400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2663000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2329300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1988600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2046200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2578500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2783900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2957100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2770800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2200900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2113100</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>124602600</v>
+      </c>
+      <c r="E54" s="3">
         <v>127040500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>131269400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>132385900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>134817900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>148754200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>157773200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>171034600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>176450600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>124158000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>127696000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>145400000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>134683000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>113101000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>100091000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13043800</v>
+      </c>
+      <c r="E57" s="3">
         <v>13449200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14394100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14033500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11179500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13240600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12396800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13834300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15056500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10639700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10875700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13259000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13849100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10622400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12450400</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22648700</v>
+      </c>
+      <c r="E58" s="3">
         <v>24442000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16185100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21677400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>24767300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>29869000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>43623500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>34136100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>26185100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>21233200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>23968000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24225800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>18574000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>15754000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12029300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7640300</v>
+      </c>
+      <c r="E59" s="3">
         <v>8326800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7474500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7493500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7399800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8016500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9135000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10681100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11324300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15672600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14873000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17256400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15092100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12285700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12993200</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>51094600</v>
+      </c>
+      <c r="E60" s="3">
         <v>53891800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>45796400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>50922500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>50588900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>60817700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>74954400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>69763800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>63503500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>47545400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>49716800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>54741200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47515200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38662100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>37472900</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14306500</v>
+      </c>
+      <c r="E61" s="3">
         <v>7853000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12030500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12224200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11837000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12959100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1436100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1633700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1800700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31121000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27491500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>32679800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>33202700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27694100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22577800</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4399800</v>
+      </c>
+      <c r="E62" s="3">
         <v>4497000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4451900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4307500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4624000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5138300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5345500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5706000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5729800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10664600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12703500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13219300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11174100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10060700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8852700</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91637200</v>
+      </c>
+      <c r="E66" s="3">
         <v>90677100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>88490400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>90145800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>93399700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>109514900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>116651500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>120285500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>122764700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>91386100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>92991300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>104142000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>94919100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>79156400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>71623400</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18053800</v>
+      </c>
+      <c r="E72" s="3">
         <v>22808200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28333000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30450200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>31650800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>32820700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>38336100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>44779200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>46341700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>29315800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>30511600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>32534600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>32326100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>29590600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>27202200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30181300</v>
+      </c>
+      <c r="E76" s="3">
         <v>33112600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>39548800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>38627600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>37720900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35665700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>37771500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47853800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>50824300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>32771500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34705000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41257100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>39764100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>33944500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28468000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3352700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4480200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2820700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1669200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1774900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4057000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6238000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2880000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7032600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4472000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3850200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3903100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3563600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3100800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3086600</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1654000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2450200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2316900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2511900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2436600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2336500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3569800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3481100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3657300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5514300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5984500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6434000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5983300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4986900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5057800</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4997800</v>
+      </c>
+      <c r="E89" s="3">
         <v>5033000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6352800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9185400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6976500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11960200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11020700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13093500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10086600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9037800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6859500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5931500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6681800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3750900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6296900</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10275300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12766400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10761800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8526800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9255100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10690000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14675100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15533500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17224800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12115700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14091700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13510900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14252500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10596200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9277500</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5750100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6485700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5372800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3362900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1209200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3337500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6586200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10229600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10806600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9285200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9035200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8717900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9896600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7617800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6192900</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>374700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>388500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>147200</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>1400100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1941200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1860000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1232100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1155700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1126400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1055800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-857200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-567200</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>326400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1758000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-869700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5044700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8997900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5783900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1445100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1147400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>346600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2160900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3900000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2097500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3635800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3943400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2788500</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>849100</v>
+      </c>
+      <c r="E101" s="3">
         <v>170900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>629000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>845800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1194300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>695600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-408500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-345300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>42700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-235100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-331500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>432100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>685600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>459500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-141300</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>423200</v>
+      </c>
+      <c r="E102" s="3">
         <v>476200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>739300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1623600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2036200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3534500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2581000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1371200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-330700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1678500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1392700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-256800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1106700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>535900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2825700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
